--- a/src/test/resources/Goldbharath Automation Excel.xlsx
+++ b/src/test/resources/Goldbharath Automation Excel.xlsx
@@ -1,18 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="8400" windowHeight="6795"/>
+    <workbookView windowWidth="28800" windowHeight="12450" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="User" sheetId="2" r:id="rId2"/>
     <sheet name="Admin" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A49:E68"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
   <si>
     <t>Gold Bharath</t>
   </si>
@@ -291,16 +290,35 @@
   </si>
   <si>
     <t>Admin</t>
+  </si>
+  <si>
+    <t>Delivery Message</t>
+  </si>
+  <si>
+    <t>asdfghjxc djyhfkhfkjf hfkytfufyv hvukyfulygjkb jyfgluigiugjk</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -323,13 +341,6 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -374,8 +385,152 @@
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -384,24 +539,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39994506668294322"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -409,38 +738,325 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -698,34 +1314,33 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.7809523809524" customWidth="1"/>
+    <col min="2" max="2" width="23.552380952381" customWidth="1"/>
+    <col min="3" max="3" width="16.4380952380952" customWidth="1"/>
+    <col min="5" max="5" width="20.8857142857143" customWidth="1"/>
     <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="8" max="8" width="32.28515625" customWidth="1"/>
+    <col min="8" max="8" width="32.2190476190476" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
-    <col min="11" max="11" width="32.28515625" customWidth="1"/>
+    <col min="10" max="10" width="8.78095238095238" customWidth="1"/>
+    <col min="11" max="11" width="32.2190476190476" customWidth="1"/>
     <col min="12" max="12" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.25">
-      <c r="E1" s="4" t="s">
+    <row r="1" ht="23.25" spans="5:5">
+      <c r="E1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -733,7 +1348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -741,7 +1356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -749,19 +1364,19 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>10</v>
       </c>
     </row>
@@ -769,10 +1384,10 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="11"/>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
@@ -781,141 +1396,141 @@
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="11"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="J9" s="11"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="5" t="s">
+      <c r="J8" s="12"/>
+    </row>
+    <row r="9" spans="10:10">
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="11"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11" s="12" t="s">
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="11"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12" s="12" t="s">
+      <c r="J11" s="12"/>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="11"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="12" t="s">
+      <c r="J12" s="12"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="11"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="12" t="s">
+      <c r="J13" s="12"/>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="12" t="s">
+    <row r="15" spans="2:2">
+      <c r="B15" s="13" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="12" t="s">
+    <row r="16" spans="2:2">
+      <c r="B16" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="12" t="s">
+    <row r="17" spans="2:2">
+      <c r="B17" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="12" t="s">
+    <row r="18" spans="2:2">
+      <c r="B18" s="13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="12" t="s">
+    <row r="19" spans="2:2">
+      <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="12" t="s">
+    <row r="20" spans="2:2">
+      <c r="B20" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="12" t="s">
+    <row r="21" spans="2:2">
+      <c r="B21" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="12" t="s">
+    <row r="22" spans="2:2">
+      <c r="B22" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="12" t="s">
+    <row r="23" spans="2:2">
+      <c r="B23" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="12" t="s">
+    <row r="24" spans="2:2">
+      <c r="B24" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="12" t="s">
+    <row r="25" spans="2:2">
+      <c r="B25" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="12" t="s">
+    <row r="26" spans="2:2">
+      <c r="B26" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="12" t="s">
+    <row r="27" spans="2:2">
+      <c r="B27" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="12" t="s">
+    <row r="28" spans="2:2">
+      <c r="B28" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="12" t="s">
+    <row r="29" spans="2:2">
+      <c r="B29" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="2:8">
-      <c r="B30" s="12" t="s">
+    <row r="30" spans="2:2">
+      <c r="B30" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:8">
-      <c r="C31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="H31" s="6"/>
-    </row>
-    <row r="32" spans="2:8" ht="28.5">
-      <c r="G32" s="7" t="s">
+    <row r="31" spans="3:8">
+      <c r="C31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="H31" s="7"/>
+    </row>
+    <row r="32" ht="28.5" spans="7:7">
+      <c r="G32" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="2:12" s="3" customFormat="1">
-      <c r="B33" s="3" t="s">
+    <row r="33" s="4" customFormat="1" spans="2:11">
+      <c r="B33" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="K33" s="4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -932,13 +1547,13 @@
       <c r="F35" t="s">
         <v>44</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="9" t="s">
         <v>45</v>
       </c>
       <c r="I35" t="s">
         <v>44</v>
       </c>
-      <c r="K35" s="8" t="s">
+      <c r="K35" s="9" t="s">
         <v>45</v>
       </c>
       <c r="L35" t="s">
@@ -955,19 +1570,19 @@
       <c r="E36" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="I36" s="12" t="s">
+      <c r="I36" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K36" s="8" t="s">
+      <c r="K36" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="L36" s="12" t="s">
+      <c r="L36" s="13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -975,25 +1590,25 @@
       <c r="B37" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>50</v>
       </c>
       <c r="E37" t="s">
         <v>51</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="I37" s="12" t="s">
+      <c r="I37" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K37" s="8" t="s">
+      <c r="K37" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="12" t="s">
+      <c r="L37" s="13" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1010,13 +1625,13 @@
       <c r="F38" t="s">
         <v>57</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="9" t="s">
         <v>58</v>
       </c>
       <c r="I38" t="s">
         <v>57</v>
       </c>
-      <c r="K38" s="8" t="s">
+      <c r="K38" s="9" t="s">
         <v>58</v>
       </c>
       <c r="L38" t="s">
@@ -1027,7 +1642,7 @@
       <c r="B39" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="13" t="s">
         <v>60</v>
       </c>
       <c r="E39" t="s">
@@ -1036,13 +1651,13 @@
       <c r="F39" t="s">
         <v>50</v>
       </c>
-      <c r="H39" s="8" t="s">
+      <c r="H39" s="9" t="s">
         <v>62</v>
       </c>
       <c r="I39" t="s">
         <v>63</v>
       </c>
-      <c r="K39" s="8" t="s">
+      <c r="K39" s="9" t="s">
         <v>62</v>
       </c>
       <c r="L39" t="s">
@@ -1062,13 +1677,13 @@
       <c r="F40" t="s">
         <v>67</v>
       </c>
-      <c r="H40" s="8" t="s">
+      <c r="H40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="I40" t="s">
         <v>50</v>
       </c>
-      <c r="K40" s="8" t="s">
+      <c r="K40" s="9" t="s">
         <v>68</v>
       </c>
       <c r="L40" t="s">
@@ -1088,95 +1703,95 @@
       <c r="F41" t="s">
         <v>55</v>
       </c>
-      <c r="H41" s="8" t="s">
+      <c r="H41" s="9" t="s">
         <v>70</v>
       </c>
       <c r="I41" t="s">
         <v>67</v>
       </c>
-      <c r="K41" s="8" t="s">
+      <c r="K41" s="9" t="s">
         <v>70</v>
       </c>
       <c r="L41" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="2:12">
+    <row r="42" spans="5:12">
       <c r="E42" t="s">
         <v>71</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="H42" s="8" t="s">
+      <c r="H42" s="9" t="s">
         <v>54</v>
       </c>
       <c r="I42" t="s">
         <v>55</v>
       </c>
-      <c r="K42" s="8" t="s">
+      <c r="K42" s="9" t="s">
         <v>54</v>
       </c>
       <c r="L42" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="2:12">
+    <row r="43" spans="5:12">
       <c r="E43" t="s">
         <v>64</v>
       </c>
       <c r="F43" t="s">
         <v>65</v>
       </c>
-      <c r="H43" s="8" t="s">
+      <c r="H43" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I43" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="K43" s="8" t="s">
+      <c r="K43" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="L43" s="12" t="s">
+      <c r="L43" s="13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="2:12">
+    <row r="44" spans="5:12">
       <c r="E44" t="s">
         <v>69</v>
       </c>
       <c r="F44" t="s">
         <v>44</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="10" t="s">
         <v>64</v>
       </c>
       <c r="I44" t="s">
         <v>65</v>
       </c>
-      <c r="K44" s="9" t="s">
+      <c r="K44" s="10" t="s">
         <v>64</v>
       </c>
       <c r="L44" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="2:12">
-      <c r="H45" s="9" t="s">
+    <row r="45" spans="8:12">
+      <c r="H45" s="10" t="s">
         <v>69</v>
       </c>
       <c r="I45" t="s">
         <v>73</v>
       </c>
-      <c r="K45" s="9" t="s">
+      <c r="K45" s="10" t="s">
         <v>69</v>
       </c>
       <c r="L45" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="48" spans="2:12">
-      <c r="E48" s="10" t="s">
+    <row r="48" spans="5:5">
+      <c r="E48" s="11" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1184,7 +1799,7 @@
       <c r="A49" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1192,75 +1807,92 @@
       <c r="A50" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="13" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15.75" spans="1:1">
+      <c r="A1" s="2" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.75">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.75">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:1">
+      <c r="A3" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.75">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.75">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.75">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" s="3" t="s">
         <v>85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="59.1428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/src/test/resources/Goldbharath Automation Excel.xlsx
+++ b/src/test/resources/Goldbharath Automation Excel.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="95">
   <si>
     <t>Gold Bharath</t>
   </si>
@@ -295,7 +295,25 @@
     <t>Delivery Message</t>
   </si>
   <si>
-    <t>asdfghjxc djyhfkhfkjf hfkytfufyv hvukyfulygjkb jyfgluigiugjk</t>
+    <t>Your gold order has been securely packed and dispatched. It will be delivered to your registered address within the scheduled delivery date. Please keep your order ID and valid identification ready at the time of delivery.</t>
+  </si>
+  <si>
+    <t>Update Delivery Details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name </t>
+  </si>
+  <si>
+    <t>Phone Number</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>ID Number</t>
+  </si>
+  <si>
+    <t>TXN202610140001</t>
   </si>
 </sst>
 </file>
@@ -984,9 +1002,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="distributed"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1320,7 +1342,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7809523809524" customWidth="1"/>
@@ -1336,7 +1358,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.25" spans="5:5">
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
@@ -1368,7 +1390,7 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="15" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1376,7 +1398,7 @@
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1384,10 +1406,10 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="12"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
@@ -1396,141 +1418,141 @@
       <c r="B8" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="12"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" spans="10:10">
-      <c r="J9" s="12"/>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" spans="2:10">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="12"/>
+      <c r="J10" s="14"/>
     </row>
     <row r="11" spans="2:10">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="12"/>
+      <c r="J11" s="14"/>
     </row>
     <row r="12" spans="2:10">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="12"/>
+      <c r="J12" s="14"/>
     </row>
     <row r="13" spans="2:10">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="12"/>
+      <c r="J13" s="14"/>
     </row>
     <row r="14" spans="2:2">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="15" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="2:2">
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="15" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="2:2">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="2:2">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="15" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="19" spans="2:2">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="2:2">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="21" spans="2:2">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="23" spans="2:2">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="15" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" spans="2:2">
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="15" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="26" spans="2:2">
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="27" spans="2:2">
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="28" spans="2:2">
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="29" spans="2:2">
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="30" spans="2:2">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="15" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="31" spans="3:8">
-      <c r="C31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="C31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="H31" s="9"/>
     </row>
     <row r="32" ht="28.5" spans="7:7">
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="10" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="33" s="4" customFormat="1" spans="2:11">
-      <c r="B33" s="4" t="s">
+    <row r="33" s="6" customFormat="1" spans="2:11">
+      <c r="B33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K33" s="4" t="s">
+      <c r="K33" s="6" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1547,13 +1569,13 @@
       <c r="F35" t="s">
         <v>44</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="11" t="s">
         <v>45</v>
       </c>
       <c r="I35" t="s">
         <v>44</v>
       </c>
-      <c r="K35" s="9" t="s">
+      <c r="K35" s="11" t="s">
         <v>45</v>
       </c>
       <c r="L35" t="s">
@@ -1570,19 +1592,19 @@
       <c r="E36" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I36" s="13" t="s">
+      <c r="I36" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K36" s="9" t="s">
+      <c r="K36" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L36" s="13" t="s">
+      <c r="L36" s="15" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1590,25 +1612,25 @@
       <c r="B37" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E37" t="s">
         <v>51</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="K37" s="9" t="s">
+      <c r="K37" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="13" t="s">
+      <c r="L37" s="15" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1625,13 +1647,13 @@
       <c r="F38" t="s">
         <v>57</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="11" t="s">
         <v>58</v>
       </c>
       <c r="I38" t="s">
         <v>57</v>
       </c>
-      <c r="K38" s="9" t="s">
+      <c r="K38" s="11" t="s">
         <v>58</v>
       </c>
       <c r="L38" t="s">
@@ -1642,7 +1664,7 @@
       <c r="B39" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="15" t="s">
         <v>60</v>
       </c>
       <c r="E39" t="s">
@@ -1651,13 +1673,13 @@
       <c r="F39" t="s">
         <v>50</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="11" t="s">
         <v>62</v>
       </c>
       <c r="I39" t="s">
         <v>63</v>
       </c>
-      <c r="K39" s="9" t="s">
+      <c r="K39" s="11" t="s">
         <v>62</v>
       </c>
       <c r="L39" t="s">
@@ -1677,13 +1699,13 @@
       <c r="F40" t="s">
         <v>67</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="11" t="s">
         <v>68</v>
       </c>
       <c r="I40" t="s">
         <v>50</v>
       </c>
-      <c r="K40" s="9" t="s">
+      <c r="K40" s="11" t="s">
         <v>68</v>
       </c>
       <c r="L40" t="s">
@@ -1703,13 +1725,13 @@
       <c r="F41" t="s">
         <v>55</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="I41" t="s">
         <v>67</v>
       </c>
-      <c r="K41" s="9" t="s">
+      <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" t="s">
@@ -1720,16 +1742,16 @@
       <c r="E42" t="s">
         <v>71</v>
       </c>
-      <c r="F42" s="13" t="s">
+      <c r="F42" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="11" t="s">
         <v>54</v>
       </c>
       <c r="I42" t="s">
         <v>55</v>
       </c>
-      <c r="K42" s="9" t="s">
+      <c r="K42" s="11" t="s">
         <v>54</v>
       </c>
       <c r="L42" t="s">
@@ -1743,16 +1765,16 @@
       <c r="F43" t="s">
         <v>65</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I43" s="13" t="s">
+      <c r="I43" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="K43" s="9" t="s">
+      <c r="K43" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="L43" s="13" t="s">
+      <c r="L43" s="15" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1763,13 +1785,13 @@
       <c r="F44" t="s">
         <v>44</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="12" t="s">
         <v>64</v>
       </c>
       <c r="I44" t="s">
         <v>65</v>
       </c>
-      <c r="K44" s="10" t="s">
+      <c r="K44" s="12" t="s">
         <v>64</v>
       </c>
       <c r="L44" t="s">
@@ -1777,13 +1799,13 @@
       </c>
     </row>
     <row r="45" spans="8:12">
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="12" t="s">
         <v>69</v>
       </c>
       <c r="I45" t="s">
         <v>73</v>
       </c>
-      <c r="K45" s="10" t="s">
+      <c r="K45" s="12" t="s">
         <v>69</v>
       </c>
       <c r="L45" t="s">
@@ -1791,7 +1813,7 @@
       </c>
     </row>
     <row r="48" spans="5:5">
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1799,7 +1821,7 @@
       <c r="A49" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="15" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1807,9 +1829,12 @@
       <c r="A50" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="15" t="s">
         <v>78</v>
       </c>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1828,37 +1853,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="5" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1871,11 +1896,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="59.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="43.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1883,12 +1908,41 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" ht="90" spans="1:2">
       <c r="A3" t="s">
         <v>87</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
